--- a/Resultados/RGAA/tri_rgaa_RC daños a cosas.xlsx
+++ b/Resultados/RGAA/tri_rgaa_RC daños a cosas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alex\Documents\Python Script\Github\IBNR-NIIF-17\Resultados\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documentos\Python_script\Github\IBNR-NIIF-17\Resultados\RGAA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80D920FD-5658-4973-A831-21123F4B6D81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B98417D1-4F6C-46D3-8EC4-D4E75063648E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="1500" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,8 +42,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy"/>
+    <numFmt numFmtId="167" formatCode="0.0000"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -183,7 +184,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -191,15 +192,22 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -503,15 +511,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B8:H24"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="8" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B8" s="11" t="s">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B8" s="9" t="s">
         <v>0</v>
       </c>
       <c r="C8" s="1">
@@ -533,129 +541,135 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B9" s="2">
         <v>43101</v>
       </c>
-      <c r="C9" s="3">
-        <v>783.09832496605554</v>
-      </c>
-      <c r="D9" s="4">
-        <v>967.3085771352296</v>
-      </c>
-      <c r="E9" s="4">
-        <v>987.45714050285142</v>
-      </c>
-      <c r="F9" s="4">
-        <v>1026.492579966729</v>
-      </c>
-      <c r="G9" s="4">
-        <v>1040.920526083097</v>
-      </c>
-      <c r="H9" s="5">
-        <v>1050.9423031129511</v>
-      </c>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C9" s="10">
+        <v>658.35473428593218</v>
+      </c>
+      <c r="D9" s="11">
+        <v>824.17455864793453</v>
+      </c>
+      <c r="E9" s="11">
+        <v>840.90265889443765</v>
+      </c>
+      <c r="F9" s="11">
+        <v>870.68431131453781</v>
+      </c>
+      <c r="G9" s="11">
+        <v>880.83662731798256</v>
+      </c>
+      <c r="H9" s="12">
+        <v>887.56050124498256</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" s="2">
         <v>43466</v>
       </c>
-      <c r="C10" s="6">
-        <v>639.28815011839686</v>
-      </c>
-      <c r="D10">
-        <v>760.24846942771615</v>
-      </c>
-      <c r="E10">
-        <v>804.5563647182845</v>
-      </c>
-      <c r="F10">
-        <v>801.88994895952237</v>
-      </c>
-      <c r="G10">
-        <v>813.03049648893818</v>
-      </c>
-      <c r="H10" s="7"/>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C10" s="13">
+        <v>575.46552116973487</v>
+      </c>
+      <c r="D10" s="14">
+        <v>675.89135850297691</v>
+      </c>
+      <c r="E10" s="14">
+        <v>709.69557219015735</v>
+      </c>
+      <c r="F10" s="14">
+        <v>707.81933179106079</v>
+      </c>
+      <c r="G10" s="14">
+        <v>715.29381828606074</v>
+      </c>
+      <c r="H10" s="15"/>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" s="2">
         <v>43831</v>
       </c>
-      <c r="C11" s="6">
-        <v>636.68419237658918</v>
-      </c>
-      <c r="D11">
-        <v>795.50973975874342</v>
-      </c>
-      <c r="E11">
-        <v>827.19386790433498</v>
-      </c>
-      <c r="F11">
-        <v>833.96204787301167</v>
-      </c>
-      <c r="H11" s="7"/>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C11" s="13">
+        <v>528.59932497988848</v>
+      </c>
+      <c r="D11" s="14">
+        <v>649.77350189531967</v>
+      </c>
+      <c r="E11" s="14">
+        <v>672.06824008142553</v>
+      </c>
+      <c r="F11" s="14">
+        <v>676.60919012342549</v>
+      </c>
+      <c r="G11" s="14"/>
+      <c r="H11" s="15"/>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" s="2">
         <v>44197</v>
       </c>
-      <c r="C12" s="6">
-        <v>779.48073170384362</v>
-      </c>
-      <c r="D12">
-        <v>910.41829791103385</v>
-      </c>
-      <c r="E12">
-        <v>944.04307322647105</v>
-      </c>
-      <c r="H12" s="7"/>
-    </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C12" s="13">
+        <v>594.69611559647774</v>
+      </c>
+      <c r="D12" s="14">
+        <v>686.83116643016683</v>
+      </c>
+      <c r="E12" s="14">
+        <v>709.39091300716689</v>
+      </c>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="15"/>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" s="2">
         <v>44562</v>
       </c>
-      <c r="C13" s="6">
-        <v>614.77831671778563</v>
-      </c>
-      <c r="D13">
-        <v>708.55640285746904</v>
-      </c>
-      <c r="H13" s="7"/>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="C13" s="13">
+        <v>432.59267071310938</v>
+      </c>
+      <c r="D13" s="14">
+        <v>495.51085642410942</v>
+      </c>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="15"/>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B14" s="2">
         <v>44927</v>
       </c>
-      <c r="C14" s="8">
-        <v>534.07327667766071</v>
-      </c>
-      <c r="D14" s="9"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9"/>
-      <c r="H14" s="10"/>
-    </row>
-    <row r="19" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C19" s="5">
+      <c r="C14" s="16">
+        <v>358.323815174</v>
+      </c>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="18"/>
+    </row>
+    <row r="19" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C19" s="4">
         <v>1050.9423031129511</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19" s="3">
         <v>967.3085771352296</v>
       </c>
-      <c r="E19" s="4">
+      <c r="E19" s="3">
         <v>987.45714050285142</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="3">
         <v>1026.492579966729</v>
       </c>
-      <c r="G19" s="4">
+      <c r="G19" s="3">
         <v>1040.920526083097</v>
       </c>
-      <c r="H19" s="5">
+      <c r="H19" s="4">
         <v>1050.9423031129511</v>
       </c>
     </row>
-    <row r="20" spans="3:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C20">
         <v>813.03049648893818</v>
       </c>
@@ -671,9 +685,9 @@
       <c r="G20">
         <v>813.03049648893818</v>
       </c>
-      <c r="H20" s="7"/>
-    </row>
-    <row r="21" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C21">
         <v>833.96204787301167</v>
       </c>
@@ -686,9 +700,9 @@
       <c r="F21">
         <v>833.96204787301167</v>
       </c>
-      <c r="H21" s="7"/>
-    </row>
-    <row r="22" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="H21" s="5"/>
+    </row>
+    <row r="22" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C22">
         <v>944.04307322647105</v>
       </c>
@@ -698,26 +712,26 @@
       <c r="E22">
         <v>944.04307322647105</v>
       </c>
-      <c r="H22" s="7"/>
-    </row>
-    <row r="23" spans="3:8" x14ac:dyDescent="0.3">
+      <c r="H22" s="5"/>
+    </row>
+    <row r="23" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C23">
         <v>708.55640285746904</v>
       </c>
       <c r="D23">
         <v>708.55640285746904</v>
       </c>
-      <c r="H23" s="7"/>
-    </row>
-    <row r="24" spans="3:8" x14ac:dyDescent="0.3">
-      <c r="C24" s="8">
+      <c r="H23" s="5"/>
+    </row>
+    <row r="24" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C24" s="6">
         <v>534.07327667766071</v>
       </c>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9"/>
-      <c r="H24" s="10"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+      <c r="H24" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
